--- a/feedback_forms/006_favorite_notification_feedback--feedback_forms.xlsx
+++ b/feedback_forms/006_favorite_notification_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>favorite_notification_time</t>
+          <t>favorite_notification_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Favorite Notification Time</t>
+          <t>Favorite Notification Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>favorite_notification_method</t>
+          <t>favorite_notification_method_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Favorite Notification Method</t>
+          <t>Favorite Notification Method 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no_notifications</t>
+          <t>no_notifications_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No Notifications</t>
+          <t>No Notifications 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>favorite_notification_method_choices</t>
+          <t>favorite_notification_method_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>favorite_notification_method_choices</t>
+          <t>favorite_notification_method_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>favorite_notification_method_choices</t>
+          <t>favorite_notification_method_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>favorite_notification_method_choices</t>
+          <t>favorite_notification_method_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>no_notifications_choices</t>
+          <t>no_notifications_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>no_notifications_choices</t>
+          <t>no_notifications_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>no_notifications_choices</t>
+          <t>no_notifications_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>no_notifications_choices</t>
+          <t>no_notifications_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
